--- a/report/项目执行计划1.xlsx
+++ b/report/项目执行计划1.xlsx
@@ -7,8 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="计划总览" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="周计划明细" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="计划总览" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="周计划明细" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="32">
+  <fonts count="33">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -46,8 +47,14 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
+      <color rgb="001d4ed8"/>
+      <sz val="8.800000000000001"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
       <color rgb="0064748b"/>
-      <sz val="9.5"/>
+      <sz val="9.199999999999999"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -58,7 +65,7 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="000F172A"/>
-      <sz val="9.199999999999999"/>
+      <sz val="9"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -68,53 +75,59 @@
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="001E3A8A"/>
-      <sz val="8.5"/>
+      <sz val="8.300000000000001"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00B45309"/>
-      <sz val="8.199999999999999"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <color rgb="00059669"/>
-      <sz val="8.199999999999999"/>
+      <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00059669"/>
-      <sz val="9.5"/>
+      <sz val="9.199999999999999"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="000284c7"/>
-      <sz val="9.5"/>
+      <sz val="9.199999999999999"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00d97706"/>
-      <sz val="9.5"/>
+      <sz val="9.199999999999999"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="00dc2626"/>
-      <sz val="9.5"/>
+      <sz val="9.199999999999999"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="007c3aed"/>
-      <sz val="9.5"/>
+      <sz val="8.800000000000001"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00ea580c"/>
-      <sz val="9.5"/>
+      <color rgb="007c3aed"/>
+      <sz val="9.199999999999999"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="0015803d"/>
+      <sz val="9.199999999999999"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -130,29 +143,19 @@
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
+      <color rgb="001d4ed8"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
       <color rgb="0064748b"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="000F172A"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
       <color rgb="001E3A8A"/>
       <sz val="8.199999999999999"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00B45309"/>
-      <sz val="8"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00059669"/>
-      <sz val="8"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -192,16 +195,22 @@
       <name val="Microsoft YaHei"/>
       <b val="1"/>
       <color rgb="007c3aed"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007c3aed"/>
       <sz val="8.5"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <b val="1"/>
-      <color rgb="00ea580c"/>
+      <color rgb="0015803d"/>
       <sz val="8.5"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -211,6 +220,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001E3A8A"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E8FC"/>
       </patternFill>
     </fill>
     <fill>
@@ -240,12 +254,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F3E8FF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00EDE9FE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF7ED"/>
+        <fgColor rgb="00F0FDF4"/>
       </patternFill>
     </fill>
   </fills>
@@ -275,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -287,14 +306,14 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -305,8 +324,8 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -323,48 +342,51 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="22" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="30" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -732,372 +754,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
-    <col width="66" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
-    <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="32" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>B2 湖仓归档平台 · 单人执行计划（AI Vibe Coding 加速 · 先功能后文档）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>口径：1 人 × 20 周 · 功能 Scope 与团队版完全一致（8 大功能域 + CC 单系统验证）· 策略：功能全做 → 上线（W14）→ 文档/设计集中补齐（AI 反生成）· 上线即结束，无知识转移/项目关闭</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="28" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Sprint</t>
-        </is>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t>周次</t>
-        </is>
-      </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>主题 / 目标</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>核心交付物（按功能域编号）</t>
-        </is>
-      </c>
-      <c r="E4" s="3" t="inlineStr">
-        <is>
-          <t>演示 / 里程碑</t>
-        </is>
-      </c>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t>主要风险</t>
-        </is>
-      </c>
-      <c r="G4" s="3" t="inlineStr">
-        <is>
-          <t>AI 提效点 🤖</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="118" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
-        <is>
-          <t>Sprint 0
-打底</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>W1~W2</t>
-        </is>
-      </c>
-      <c r="C5" s="6" t="inlineStr">
-        <is>
-          <t>需求定稿 + 环境就绪 + CC 连接打通</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>【8 域需求】① 需求清单 + 数据流图 + 保留期矩阵 + PII 分级（AI 起稿 → 业务方一次评审定稿）② 架构定稿 + 资源申请单（区域=境内驻留）+ 平台资源验收 + UC 初始化 ③ CC 1253 表扫描分类（业务表/垃圾表/附件元数据表）④ SeaTunnel PoC：抽样 10 表 → Iceberg RAW → SQL Warehouse 可查 ⑤ 前后端骨架 + Azure DevOps Pipelines CI 就绪</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr">
-        <is>
-          <t>★ CC 端到端 PoC 跑通；BRD 一次评审通过</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>资源受理/CC 账号周期（W1 立即申请）；实时性指标未定</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>BRD/数据流图 AI 生成；表分类脚本 AI 生成；项目脚手架 AI 生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="118" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
-        <is>
-          <t>Sprint 1
-核心 MVP</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>W3~W5</t>
-        </is>
-      </c>
-      <c r="C6" s="6" t="inlineStr">
-        <is>
-          <t>01 迁移 + 05 检索 + 08 权限 端到端（CC 首批 50 表）</t>
-        </is>
-      </c>
-      <c r="D6" s="7" t="inlineStr">
-        <is>
-          <t>【01】① SeaTunnel 批量导入 50 表（分片/限速/断点）② 迁移任务管理（配置生成器+状态+对账：行数/校验和/SHA-256）【05】③ 配置化检索页（动态渲染）④ 预览（SAS 直连）+ 导出【08】⑤ RBAC 五角色 + OIDC/JWT 鉴权 + UC GRANT + 掩码函数（权限三态）【06】⑥ 审计埋点 v1【07】⑦ JDBC 连接器模板 v1（SQL Server）【安全】⑧ 依赖扫描+SAST 进 CI</t>
-        </is>
-      </c>
-      <c r="E6" s="8" t="inlineStr">
-        <is>
-          <t>★ W5：CC 50 表全链路——登录→检索→预览→导出，带权限与审计</t>
-        </is>
-      </c>
-      <c r="F6" s="9" t="inlineStr">
-        <is>
-          <t>一人串行无并行；掩码函数/权限三态是硬骨头；AI 提效若不及预期在此暴露</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>CRUD/鉴权/前端组件 AI 全生成（×3）；测试用例 AI 生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="118" customHeight="1">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Sprint 2
-治理与安全</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>W6~W8</t>
-        </is>
-      </c>
-      <c r="C7" s="6" t="inlineStr">
-        <is>
-          <t>02 治理 + 03 生命周期 + 04 安全管控</t>
-        </is>
-      </c>
-      <c r="D7" s="7" t="inlineStr">
-        <is>
-          <t>【02】① 增量接入（watermark）② 冷数据识别与自动转冷 ③ 元数据标准管理界面【03】④ 到期处置引擎（扫描→DROP PARTITION→VACUUM）⑤ Legal Hold（Hold/Release+豁免+留痕）⑥ 归档模型管理【04】⑦ 加密（CMK+字段级+轮转）⑧ 脱敏（COLUMN MASK）⑨ 境内驻留核查 ⑩ ADLS 分层与生命周期规则 + Compaction【安全】⑪ gitleaks/Trivy 门禁③④上线；处置全链路自测</t>
-        </is>
-      </c>
-      <c r="E7" s="8" t="inlineStr">
-        <is>
-          <t>★ W8：处置全链路（1 天保留期→到期→Hold 拦截→处置→审计）+ 四道安全门禁全开</t>
-        </is>
-      </c>
-      <c r="F7" s="9" t="inlineStr">
-        <is>
-          <t>处置不可逆需充分自测；加密/驻留核查必须人工验证（AI 只能辅助）</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>处置/Hold 界面 AI 生成；Spark SQL 转换 AI 辅助；配置模板 AI 生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="118" customHeight="1">
-      <c r="A8" s="13" t="inlineStr">
-        <is>
-          <t>Sprint 3
-CC 全量</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>W9~W11</t>
-        </is>
-      </c>
-      <c r="C8" s="6" t="inlineStr">
-        <is>
-          <t>CC 1253 表全量迁移 + 07 连接器库 + 06 合规报表</t>
-        </is>
-      </c>
-      <c r="D8" s="7" t="inlineStr">
-        <is>
-          <t>【01】① CC 全量分批迁移（剔除垃圾表后约 600~800 张，分 5~8 批，批次自动执行人盯异常）② 逐批对账 + 全量对账报告【07】③ 连接器模板库（MySQL+文件源，AI 复用改写）④ 连接器运行监控与审计【06】⑤ 合规报表（审计查询+等保/个保法对照+导出）【08】⑥ 行级隔离验证（越权全过）</t>
-        </is>
-      </c>
-      <c r="E8" s="8" t="inlineStr">
-        <is>
-          <t>★ W11：CC 全量对账 100% + 连接器模板演示（新源 30 分钟接入）</t>
-        </is>
-      </c>
-      <c r="F8" s="9" t="inlineStr">
-        <is>
-          <t>全量迁移时长不可控（数据量未知，W9 前 sp_spaceused 实测）；批次失败重跑</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>模板 AI 改写 ×2；报表页面 AI 生成；越权用例 AI 生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="118" customHeight="1">
-      <c r="A9" s="14" t="inlineStr">
-        <is>
-          <t>Sprint 4
-生产上线</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>W12~W14</t>
-        </is>
-      </c>
-      <c r="C9" s="6" t="inlineStr">
-        <is>
-          <t>生产部署 + UAT + 审批 → Go-Live</t>
-        </is>
-      </c>
-      <c r="D9" s="7" t="inlineStr">
-        <is>
-          <t>① 生产发布（Helm 生产版 + UC 权限/掩码/生命周期/驻留核查脚本）② CC 生产全量迁移（分批+对账）③ 安全四门禁生产终检 + 渗透配合 ④ UAT（8 域场景：迁移对账/检索/预览导出/脱敏三态/处置/Legal Hold/审计报表/SSO）⑤ 审批材料包（AI 起稿）+ 提交 ⑥ Go-Live + 48h 值守</t>
-        </is>
-      </c>
-      <c r="E9" s="8" t="inlineStr">
-        <is>
-          <t>★ W14：Go-Live + UAT 签字 + 审批受理</t>
-        </is>
-      </c>
-      <c r="F9" s="9" t="inlineStr">
-        <is>
-          <t>UAT 业务方排期；审批周期；CC 生产迁移跨窗口</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>审批材料/安全说明 AI 起草 ×3；部署脚本 AI 生成</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="118" customHeight="1">
-      <c r="A10" s="15" t="inlineStr">
-        <is>
-          <t>Sprint 5
-文档补齐</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>W15~W17</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>文档与设计集中补齐（上线后）</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>① 架构图×4（C4 上下文/容器/组件/部署）+ 数据流图——AI 从代码与配置反生成 ② 详细设计×3（应用/数据/安全）——从 git 提交记录与 ADR 还原 ③ 接口文档（OpenAPI 自动导出）④ 数据字典（35 表+湖仓四层，脚本导出）⑤ 用户手册（含截图）⑥ 运维手册（部署/监控/故障/备份恢复）⑦ 培训视频（录屏+AI 字幕）</t>
-        </is>
-      </c>
-      <c r="E10" s="8" t="inlineStr">
-        <is>
-          <t>★ W17：7 套文档终版归档</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>记忆衰减（对策：开发期保持提交记录+一句话 ADR）；文档口径需业务方确认</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>文档 AI 反生成 ×3~5（全计划最大提效区）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="118" customHeight="1">
-      <c r="A11" s="16" t="inlineStr">
-        <is>
-          <t>Sprint 6
-缓冲收尾</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>W18~W20</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>缓冲 + 遗留清零 + 收尾</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>① 进度缓冲：吸收全量迁移/UAT/审批任一延期（约 17%）② 无延期则：遗留 Bug 清零 + 性能打磨 ③ 交付物版本 tag（代码/脚本/文档）④ 最终自查（8 域功能 + 7 套文档 + Checklist）→ 项目结束</t>
-        </is>
-      </c>
-      <c r="E11" s="8" t="inlineStr">
-        <is>
-          <t>★ W20：项目结束</t>
-        </is>
-      </c>
-      <c r="F11" s="9" t="inlineStr">
-        <is>
-          <t>单人单点风险（请假/生病即停摆）；建议 W5 校准一次 AI 提效</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>AI 辅助修复与回归</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="26" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
-        <is>
-          <t>工期推算：团队版 270 人天 ÷ AI 加权提效 ×2.2 ≈ 123 人天；串行损耗 +10%；文档延后集中 + 无会议损耗对冲 → 20 周（100 人天）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="26" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
-        <is>
-          <t>上线节奏：W14 Go-Live（团队版 W11，晚 3 周）；总人力 270 → 100 人天（↓63%）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="26" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
-        <is>
-          <t>校准点：W5 MVP 里程碑若 AI 提效不及预期（×1.5），工期拉长至 26~28 周，届时再议是否加人</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
-        <is>
-          <t>风险：单人单点（人停项目停）· 无代码评审（靠 AI 自查+测试覆盖+四道门禁兜底）· 文档后补记忆衰减（保持 ADR 习惯）</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="A13:G13"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A15:G15"/>
-  </mergeCells>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1108,90 +767,533 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F70"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="76" customWidth="1" min="3" max="3"/>
-    <col width="26" customWidth="1" min="4" max="4"/>
-    <col width="24" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="13" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="32" customWidth="1" min="7" max="7"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="18" t="inlineStr">
-        <is>
-          <t>周计划明细 · 单人 20 周（任务含 🤖 AI 提效标注 · 外部依赖为不可压缩物理时间）</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="19" t="inlineStr">
-        <is>
-          <t>角色合一：需求/架构/数据工程/全栈/QA 由 1 人承担 · 文档集中在 S5 · CC（Caring Center）单系统贯穿</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>B2 湖仓归档平台 · 单人执行计划（两个 Release · AI Vibe Coding 加速 · 先功能后文档）</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>R1 系统上线（W1~W14）：W1~W13 全部功能与上线就绪，W14 一周集中上线（发布→迁移→UAT→Go-Live）· R2 文档交付与收尾（W15~W20）：文档/设计 AI 反生成 + 缓冲收尾 · 功能 Scope 与团队版一致（8 域 + CC 单系统）</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t>Release</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
           <t>Sprint</t>
         </is>
       </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>周次</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>主题 / 目标</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>核心交付物（按功能域编号）</t>
+        </is>
+      </c>
+      <c r="F4" s="3" t="inlineStr">
+        <is>
+          <t>演示 / 里程碑</t>
+        </is>
+      </c>
+      <c r="G4" s="3" t="inlineStr">
+        <is>
+          <t>主要风险</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>AI 提效点 🤖</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="122" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Sprint 0
+打底</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>W1~W2</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>需求定稿 + 环境就绪 + CC 连接打通</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>【8 域需求】① 需求清单 + 数据流图 + 保留期矩阵 + PII 分级（AI 起稿→一次评审定稿）② 架构定稿 + 资源申请单（区域=境内）+ 平台资源验收 + UC 初始化 ③ CC 1253 表扫描分类 ④ SeaTunnel PoC（抽样 10 表端到端）⑤ 前后端骨架 + Azure DevOps Pipelines CI</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>★ CC 端到端 PoC 跑通；BRD 一次评审通过</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>资源受理/CC 账号周期（W1 立即申请）；实时性指标未定</t>
+        </is>
+      </c>
+      <c r="H5" s="11" t="inlineStr">
+        <is>
+          <t>BRD/数据流图 AI 生成；表分类脚本；项目脚手架</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="122" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Sprint 1
+核心 MVP</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>W3~W5</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>01 迁移 + 05 检索 + 08 权限 端到端（CC 首批 50 表）</t>
+        </is>
+      </c>
+      <c r="E6" s="8" t="inlineStr">
+        <is>
+          <t>【01】① 批量导入 50 表（分片/限速/断点）② 迁移任务管理（生成器+状态+对账 SHA-256）【05】③ 配置化检索页 ④ 预览（SAS）+ 导出【08】⑤ RBAC + OIDC/JWT + UC GRANT + 掩码函数（权限三态）【06】⑥ 审计埋点【07】⑦ 连接器模板 v1【安全】⑧ 依赖扫描+SAST 进 CI</t>
+        </is>
+      </c>
+      <c r="F6" s="9" t="inlineStr">
+        <is>
+          <t>★ W5：CC 50 表全链路（登录→检索→预览→导出）</t>
+        </is>
+      </c>
+      <c r="G6" s="10" t="inlineStr">
+        <is>
+          <t>一人串行；掩码/权限三态是硬骨头；W5 为 AI 提效校准点</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr">
+        <is>
+          <t>CRUD/鉴权/前端组件 ×3；测试用例生成</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="122" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>Sprint 2
+治理与安全</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>W6~W8</t>
+        </is>
+      </c>
+      <c r="D7" s="7" t="inlineStr">
+        <is>
+          <t>02 治理 + 03 生命周期 + 04 安全管控</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>【02】① 增量接入（watermark）② 冷数据识别自动转冷 ③ 元数据标准界面【03】④ 处置引擎（扫描→DROP PARTITION→VACUUM）⑤ Legal Hold（Hold/Release+豁免+留痕）⑥ 归档模型管理【04】⑦ 加密（CMK+字段级+轮转）⑧ 脱敏 ⑨ 境内驻留核查 ⑩ 分层与 Compaction【安全】⑪ gitleaks/Trivy 门禁；处置全链路自测</t>
+        </is>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>★ W8：处置全链路（到期→Hold→处置→审计）+ 四道门禁全开</t>
+        </is>
+      </c>
+      <c r="G7" s="10" t="inlineStr">
+        <is>
+          <t>处置不可逆需充分自测；加密/驻留必须人工验证</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr">
+        <is>
+          <t>处置/Hold 界面生成；Spark SQL 辅助；配置模板</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="122" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>Sprint 3
+功能完善与就绪</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>W9~W13</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>功能收口：CC 全量 + 连接器库 + 合规报表 + 上线就绪</t>
+        </is>
+      </c>
+      <c r="E8" s="8" t="inlineStr">
+        <is>
+          <t>【01】① CC 全量 1253 表分批迁移（600~800 有效表，5~8 批）+ 逐批对账 + 全量对账报告【07】② 连接器模板库（MySQL/文件源）③ 运行监控与审计【06】④ 合规报表（等保/个保法对照+导出）【08】⑤ 行级隔离验证【就绪（W12~13）】⑥ 功能打磨/性能/遗留清零 ⑦ 🤖生产发布包（Helm 生产 values+UC 脚本）⑧ 🤖审批材料起稿 ⑨ UAT 预演（Staging 8 域走查）+ UAT 脚本定稿 ⑩ 安全终检（四门禁生产版+渗透）⑪ 生产迁移窗口预约与预跑</t>
+        </is>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>★ W11：CC 全量对账 100%（全部功能 Done）★ W13：上线就绪检查通过（发布包/材料/预演全绿）</t>
+        </is>
+      </c>
+      <c r="G8" s="10" t="inlineStr">
+        <is>
+          <t>全量迁移时长不可控；UAT 预演需业务方提前介入；W13 就绪检查不过则 W14 上线顺延（用 R2 缓冲）</t>
+        </is>
+      </c>
+      <c r="H8" s="11" t="inlineStr">
+        <is>
+          <t>模板 AI 改写 ×2；报表页面；审批材料起草 ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="122" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>Release 1
+系统上线</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Sprint 4
+上线周</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D9" s="7" t="inlineStr">
+        <is>
+          <t>上线周：发布 → 迁移 → UAT → Go-Live（集中一周）</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>① 生产发布执行（Azure DevOps Environments 审批，用就绪包一键发布）② CC 生产全量迁移收尾（W13 预跑后增量补齐）③ UAT 正式执行（8 域场景，业务方签字）④ P1 问题当日清 ⑤ 审批材料提交 ⑥ Go-Live 决策 + 上线 + 48h 值守</t>
+        </is>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>★ W14：Go-Live + UAT 签字 + 审批受理 → Release 1 交付</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="inlineStr">
+        <is>
+          <t>一周内完成发布+UAT+上线节奏极紧：依赖 W13 就绪检查 100% 通过；生产迁移建议 W13 晚/W14 周末窗口启动</t>
+        </is>
+      </c>
+      <c r="H9" s="11" t="inlineStr">
+        <is>
+          <t>材料/部署脚本已提前 AI 生成，本周仅执行</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="122" customHeight="1">
+      <c r="A10" s="16" t="inlineStr">
+        <is>
+          <t>Release 2
+文档交付与收尾</t>
+        </is>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>Sprint 5
+文档补齐</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>W15~W17</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>文档与设计集中补齐（上线后）</t>
+        </is>
+      </c>
+      <c r="E10" s="8" t="inlineStr">
+        <is>
+          <t>① 架构图×4（C4）+ 数据流图（AI 从代码反生成）② 详细设计×3（应用/数据/安全，从提交记录+ADR 还原）③ 接口文档（OpenAPI 自动导出）④ 数据字典（35 表+湖仓四层）⑤ 用户手册（含截图）⑥ 运维手册 ⑦ 培训视频（录屏+AI 字幕）</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>★ W17：7 套文档终版归档（Release 2 主体交付）</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>记忆衰减（对策：开发期 ADR 习惯）；文档口径需业务方确认</t>
+        </is>
+      </c>
+      <c r="H10" s="11" t="inlineStr">
+        <is>
+          <t>文档 AI 反生成 ×3~5（最大提效区）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="122" customHeight="1">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>Release 2
+文档交付与收尾</t>
+        </is>
+      </c>
+      <c r="B11" s="18" t="inlineStr">
+        <is>
+          <t>Sprint 6
+缓冲收尾</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>W18~W20</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>缓冲 + 遗留清零 + 收尾</t>
+        </is>
+      </c>
+      <c r="E11" s="8" t="inlineStr">
+        <is>
+          <t>① 缓冲：吸收全量迁移/UAT/审批/上线任一延期（约 17%）② 无延期则遗留 Bug 清零 + 性能打磨 ③ 交付物版本 tag（代码/脚本/文档）④ 最终自查（8 域功能+7 套文档+Checklist）→ 项目结束</t>
+        </is>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>★ W20：项目结束</t>
+        </is>
+      </c>
+      <c r="G11" s="10" t="inlineStr">
+        <is>
+          <t>单人单点风险；若 R1 上线顺延，本段顺延压缩</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>AI 辅助修复回归</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="26" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>两个 Release：R1（W1~W14）交付可上线的系统——W1~W13 全部功能与就绪、W14 一周集中上线；R2（W15~W20）交付文档与收尾</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="26" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>上线压缩依据：发布包/审批材料/UAT 脚本/预演全部前移到 W12~W13 完成，W14 仅执行（发布→迁移收尾→UAT→Go-Live），消除 W11~W13 与上线的重叠</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="26" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>工期口径：1 人 × 20 周 ≈ 100 人天（团队版 270 人天 ÷ AI 提效 ×2.2，串行损耗与无会议损耗对冲）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>校准点：W5（MVP）验证 AI 提效；W13（就绪检查）决定 W14 是否上线——不过则顺延用 R2 缓冲</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="26" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>风险：单人单点 · 无代码评审（AI 自查+测试+四门禁兜底）· 上线周节奏紧（依赖就绪检查 100%）</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A13:H13"/>
+    <mergeCell ref="A14:H14"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G73"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="3"/>
+    <col width="72" customWidth="1" min="4" max="4"/>
+    <col width="27" customWidth="1" min="5" max="5"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>周计划明细 · 单人 20 周 · R1 功能期 W1~W13 → W14 上线周 → R2 文档 W15~W20</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="21" t="inlineStr">
+        <is>
+          <t>🤖 = AI 提效标注 · 外部依赖为不可压缩物理时间 · CC（Caring Center）单系统贯穿 · 上线只占 W14 一周</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Release</t>
+        </is>
+      </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
+          <t>Sprint</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
           <t>Week</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>任务</t>
         </is>
       </c>
-      <c r="D4" s="3" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>产出物 / 验收标准</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>外部依赖（不可压缩）</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>AI 提效 🤖</t>
         </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 0</t>
-        </is>
-      </c>
-      <c r="B5" s="21" t="inlineStr">
+      <c r="A5" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B5" s="23" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
         <is>
           <t>W1</t>
         </is>
       </c>
-      <c r="C5" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 8 域需求清单 + 数据流图 + 保留期矩阵 + PII 分级（AI 起稿，约 W1 末发业务方预读）</t>
-        </is>
-      </c>
-      <c r="D5" s="23" t="inlineStr">
+      <c r="D5" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 8 域需求清单 + 数据流图 + 保留期矩阵 + PII 分级（AI 起稿，W1 末发业务方预读）</t>
+        </is>
+      </c>
+      <c r="E5" s="25" t="inlineStr">
         <is>
           <t>需求清单 v1；申请单已交；CC 分类清单</t>
         </is>
       </c>
-      <c r="E5" s="24" t="inlineStr">
+      <c r="F5" s="10" t="inlineStr">
         <is>
           <t>平台受理 3~5 天；CC 账号 1~2 周</t>
         </is>
       </c>
-      <c r="F5" s="25" t="inlineStr">
+      <c r="G5" s="11" t="inlineStr">
         <is>
           <t>需求成稿/分类脚本</t>
         </is>
@@ -1200,66 +1302,74 @@
     <row r="6" ht="30" customHeight="1">
       <c r="A6" s="26" t="n"/>
       <c r="B6" s="26" t="n"/>
-      <c r="C6" s="22" t="inlineStr">
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="24" t="inlineStr">
         <is>
           <t>• 资源申请单提交平台团队（AKS 命名空间/ADLS/SQL DB/Databricks/Key Vault，区域=境内）</t>
         </is>
       </c>
-      <c r="D6" s="26" t="n"/>
       <c r="E6" s="26" t="n"/>
       <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
       <c r="A7" s="26" t="n"/>
       <c r="B7" s="26" t="n"/>
-      <c r="C7" s="22" t="inlineStr">
-        <is>
-          <t>• CC 只读账号 + NAT 白名单申请（流程最长，D1 启动）</t>
-        </is>
-      </c>
-      <c r="D7" s="26" t="n"/>
+      <c r="C7" s="26" t="n"/>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>• CC 只读账号 + NAT 白名单申请（D1 启动）</t>
+        </is>
+      </c>
       <c r="E7" s="26" t="n"/>
       <c r="F7" s="26" t="n"/>
-    </row>
-    <row r="8" ht="30" customHeight="1">
+      <c r="G7" s="26" t="n"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
       <c r="A8" s="26" t="n"/>
       <c r="B8" s="26" t="n"/>
-      <c r="C8" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 CC 1253 表扫描分类脚本（information_schema → 业务表/垃圾表/附件元数据表）</t>
-        </is>
-      </c>
-      <c r="D8" s="26" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 CC 1253 表扫描分类脚本（→ 业务表/垃圾表/附件元数据表）</t>
+        </is>
+      </c>
       <c r="E8" s="26" t="n"/>
       <c r="F8" s="26" t="n"/>
+      <c r="G8" s="26" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="20" t="inlineStr">
-        <is>
-          <t>Sprint 0</t>
-        </is>
-      </c>
-      <c r="B9" s="21" t="inlineStr">
+      <c r="A9" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>S0</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
         <is>
           <t>W2</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="D9" s="24" t="inlineStr">
         <is>
           <t>• 平台交付资源验收（ADLS/SQL DB/Databricks/Key Vault 逐项连通）</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="E9" s="25" t="inlineStr">
         <is>
           <t>★ PoC 跑通；骨架+CI 就绪；需求签字</t>
         </is>
       </c>
-      <c r="E9" s="24" t="inlineStr">
+      <c r="F9" s="10" t="inlineStr">
         <is>
           <t>资源交付；业务方评审排期</t>
         </is>
       </c>
-      <c r="F9" s="25" t="inlineStr">
+      <c r="G9" s="11" t="inlineStr">
         <is>
           <t>PoC 配置/脚手架</t>
         </is>
@@ -1268,78 +1378,87 @@
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="26" t="n"/>
       <c r="B10" s="26" t="n"/>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="24" t="inlineStr">
         <is>
           <t>• 🤖 SeaTunnel PoC：抽样 10 表 → Iceberg RAW → SQL Warehouse 可查</t>
         </is>
       </c>
-      <c r="D10" s="26" t="n"/>
       <c r="E10" s="26" t="n"/>
       <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
       <c r="A11" s="26" t="n"/>
       <c r="B11" s="26" t="n"/>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C11" s="26" t="n"/>
+      <c r="D11" s="24" t="inlineStr">
         <is>
           <t>• UC 初始化：arch_cc catalog + GRANT 模板 + SP-query/SP-audit</t>
         </is>
       </c>
-      <c r="D11" s="26" t="n"/>
       <c r="E11" s="26" t="n"/>
       <c r="F11" s="26" t="n"/>
-    </row>
-    <row r="12" ht="30" customHeight="1">
+      <c r="G11" s="26" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1">
       <c r="A12" s="26" t="n"/>
       <c r="B12" s="26" t="n"/>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 前后端骨架（Clean Architecture + EF Core + React）+ Azure DevOps Pipelines CI</t>
-        </is>
-      </c>
-      <c r="D12" s="26" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 前后端骨架 + Azure DevOps Pipelines CI</t>
+        </is>
+      </c>
       <c r="E12" s="26" t="n"/>
       <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="26" t="n"/>
       <c r="B13" s="26" t="n"/>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="C13" s="26" t="n"/>
+      <c r="D13" s="24" t="inlineStr">
         <is>
           <t>• 需求评审会（一次过）：业务方确认签字</t>
         </is>
       </c>
-      <c r="D13" s="26" t="n"/>
       <c r="E13" s="26" t="n"/>
       <c r="F13" s="26" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="27" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
+      <c r="G13" s="26" t="n"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B14" s="27" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>W3</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【08】RBAC：user/role/permission/page CRUD + OIDC/JWT 鉴权中间件 + 前端权限渲染指令</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>RBAC 提测；50 表入 RAW；CI 门禁生效</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【08】RBAC：四表 CRUD + OIDC/JWT 鉴权中间件 + 前端权限渲染指令</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="inlineStr">
+        <is>
+          <t>RBAC 提测；50 表入 RAW</t>
+        </is>
+      </c>
+      <c r="F14" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F14" s="25" t="inlineStr">
+      <c r="G14" s="11" t="inlineStr">
         <is>
           <t>CRUD/鉴权/前端 ×3</t>
         </is>
@@ -1348,146 +1467,163 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="26" t="n"/>
       <c r="B15" s="26" t="n"/>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【05】配置化检索页：动态筛选/表格/分页（元数据驱动渲染）</t>
-        </is>
-      </c>
-      <c r="D15" s="26" t="n"/>
+      <c r="C15" s="26" t="n"/>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【05】配置化检索页：动态筛选/表格/分页</t>
+        </is>
+      </c>
       <c r="E15" s="26" t="n"/>
       <c r="F15" s="26" t="n"/>
+      <c r="G15" s="26" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="26" t="n"/>
       <c r="B16" s="26" t="n"/>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>• 【01】SeaTunnel 批量导入 CC 首批 50 表（分片并行/限速/断点续传）</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>• 【01】SeaTunnel 批量导入 CC 首批 50 表（分片/限速/断点）</t>
+        </is>
+      </c>
       <c r="E16" s="26" t="n"/>
       <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="26" t="n"/>
       <c r="B17" s="26" t="n"/>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 元数据库 35 表 Migration + 单测（覆盖率 &gt;70% 进 CI）</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="n"/>
+      <c r="C17" s="26" t="n"/>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 元数据库 35 表 Migration + 单测（&gt;70% 进 CI）</t>
+        </is>
+      </c>
       <c r="E17" s="26" t="n"/>
       <c r="F17" s="26" t="n"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="27" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
+      <c r="G17" s="26" t="n"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>W4</t>
         </is>
       </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>• 【01】迁移任务管理：配置生成器（勾选→.conf→K8s Job）+ 状态跟踪 + 对账（行数/校验和/SHA-256 台账）</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>任务管理可用；对账 100%；门禁上线</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>• 【01】迁移任务管理：配置生成器 + 状态跟踪 + 对账（行数/校验和/SHA-256）</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="inlineStr">
+        <is>
+          <t>任务管理可用；对账 100%</t>
+        </is>
+      </c>
+      <c r="F18" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="25" t="inlineStr">
-        <is>
-          <t>页面/埋点/门禁配置 ×3</t>
+      <c r="G18" s="11" t="inlineStr">
+        <is>
+          <t>页面/埋点/门禁 ×3</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="26" t="n"/>
       <c r="B19" s="26" t="n"/>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【05】结果预览（图片/附件 SAS 直连）+ 导出 CSV</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="n"/>
+      <c r="C19" s="26" t="n"/>
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【05】结果预览（SAS 直连）+ 导出 CSV</t>
+        </is>
+      </c>
       <c r="E19" s="26" t="n"/>
       <c r="F19" s="26" t="n"/>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="26" t="n"/>
       <c r="B20" s="26" t="n"/>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【06】审计埋点（后端拦截 → 审计表）</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【06】审计埋点（后端拦截→审计表）</t>
+        </is>
+      </c>
       <c r="E20" s="26" t="n"/>
       <c r="F20" s="26" t="n"/>
+      <c r="G20" s="26" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="26" t="n"/>
       <c r="B21" s="26" t="n"/>
-      <c r="C21" s="22" t="inlineStr">
+      <c r="C21" s="26" t="n"/>
+      <c r="D21" s="24" t="inlineStr">
         <is>
           <t>• 🤖【07】JDBC 连接器模板 v1（SQL Server 类型映射）</t>
         </is>
       </c>
-      <c r="D21" s="26" t="n"/>
       <c r="E21" s="26" t="n"/>
       <c r="F21" s="26" t="n"/>
+      <c r="G21" s="26" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="26" t="n"/>
       <c r="B22" s="26" t="n"/>
-      <c r="C22" s="22" t="inlineStr">
-        <is>
-          <t>• 安全门禁①②：依赖扫描 + SAST（CodeQL/Semgrep）进 Pipelines</t>
-        </is>
-      </c>
-      <c r="D22" s="26" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>• 安全门禁①②：依赖扫描 + SAST 进 Pipelines</t>
+        </is>
+      </c>
       <c r="E22" s="26" t="n"/>
       <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="27" t="inlineStr">
-        <is>
-          <t>Sprint 1</t>
-        </is>
-      </c>
-      <c r="B23" s="21" t="inlineStr">
+      <c r="A23" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B23" s="27" t="inlineStr">
+        <is>
+          <t>S1</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
         <is>
           <t>W5</t>
         </is>
       </c>
-      <c r="C23" s="22" t="inlineStr">
-        <is>
-          <t>• 【08】UC GRANT 落地（arch_cc）+ 掩码函数（aes_encrypt + COLUMN MASK）</t>
-        </is>
-      </c>
-      <c r="D23" s="23" t="inlineStr">
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>• 【08】UC GRANT 落地 + 掩码函数（aes_encrypt + COLUMN MASK）</t>
+        </is>
+      </c>
+      <c r="E23" s="25" t="inlineStr">
         <is>
           <t>★ CC 50 表 MVP 全通</t>
         </is>
       </c>
-      <c r="E23" s="24" t="inlineStr">
+      <c r="F23" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F23" s="25" t="inlineStr">
+      <c r="G23" s="11" t="inlineStr">
         <is>
           <t>测试用例/界面 ×3</t>
         </is>
@@ -1496,66 +1632,74 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="26" t="n"/>
       <c r="B24" s="26" t="n"/>
-      <c r="C24" s="22" t="inlineStr">
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="24" t="inlineStr">
         <is>
           <t>• 【05】SERVE 层首版（热表物化 + Z-Order）</t>
         </is>
       </c>
-      <c r="D24" s="26" t="n"/>
       <c r="E24" s="26" t="n"/>
       <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="26" t="n"/>
       <c r="B25" s="26" t="n"/>
-      <c r="C25" s="22" t="inlineStr">
-        <is>
-          <t>• 权限三态联调（明文/掩码/拒绝）+ 安全修复（High 清零）</t>
-        </is>
-      </c>
-      <c r="D25" s="26" t="n"/>
+      <c r="C25" s="26" t="n"/>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>• 权限三态联调 + 安全修复（High 清零）</t>
+        </is>
+      </c>
       <c r="E25" s="26" t="n"/>
       <c r="F25" s="26" t="n"/>
+      <c r="G25" s="26" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="26" t="n"/>
       <c r="B26" s="26" t="n"/>
-      <c r="C26" s="22" t="inlineStr">
-        <is>
-          <t>• ★ MVP 自查：登录→检索→预览→导出 全链路走通（W5 校准点：评估 AI 实际提效）</t>
-        </is>
-      </c>
-      <c r="D26" s="26" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>• ★ MVP 自查：登录→检索→预览→导出全链路（AI 提效校准点）</t>
+        </is>
+      </c>
       <c r="E26" s="26" t="n"/>
       <c r="F26" s="26" t="n"/>
+      <c r="G26" s="26" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="28" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="B27" s="21" t="inlineStr">
+      <c r="A27" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B27" s="28" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C27" s="7" t="inlineStr">
         <is>
           <t>W6</t>
         </is>
       </c>
-      <c r="C27" s="22" t="inlineStr">
-        <is>
-          <t>• 【02】增量接入：watermark 方案落地（按需求确认的实时指标）</t>
-        </is>
-      </c>
-      <c r="D27" s="23" t="inlineStr">
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>• 【02】增量接入：watermark 方案落地</t>
+        </is>
+      </c>
+      <c r="E27" s="25" t="inlineStr">
         <is>
           <t>增量自动入湖；处置引擎可跑</t>
         </is>
       </c>
-      <c r="E27" s="24" t="inlineStr">
+      <c r="F27" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F27" s="25" t="inlineStr">
+      <c r="G27" s="11" t="inlineStr">
         <is>
           <t>界面生成</t>
         </is>
@@ -1564,66 +1708,74 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="26" t="n"/>
       <c r="B28" s="26" t="n"/>
-      <c r="C28" s="22" t="inlineStr">
-        <is>
-          <t>• 【02】冷数据识别与自动转冷（访问频率 → 分层）</t>
-        </is>
-      </c>
-      <c r="D28" s="26" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>• 【02】冷数据识别与自动转冷</t>
+        </is>
+      </c>
       <c r="E28" s="26" t="n"/>
       <c r="F28" s="26" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
+      <c r="G28" s="26" t="n"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
       <c r="A29" s="26" t="n"/>
       <c r="B29" s="26" t="n"/>
-      <c r="C29" s="22" t="inlineStr">
-        <is>
-          <t>• 【03】到期处置引擎：扫描（到期计算）→ DROP PARTITION → VACUUM（原生调度）</t>
-        </is>
-      </c>
-      <c r="D29" s="26" t="n"/>
+      <c r="C29" s="26" t="n"/>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>• 【03】到期处置引擎：扫描→DROP PARTITION→VACUUM（原生调度）</t>
+        </is>
+      </c>
       <c r="E29" s="26" t="n"/>
       <c r="F29" s="26" t="n"/>
+      <c r="G29" s="26" t="n"/>
     </row>
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="26" t="n"/>
       <c r="B30" s="26" t="n"/>
-      <c r="C30" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【02】元数据标准管理界面（数据 Owner/来源/命名规范）</t>
-        </is>
-      </c>
-      <c r="D30" s="26" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【02】元数据标准管理界面</t>
+        </is>
+      </c>
       <c r="E30" s="26" t="n"/>
       <c r="F30" s="26" t="n"/>
+      <c r="G30" s="26" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="28" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
+      <c r="A31" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B31" s="28" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C31" s="7" t="inlineStr">
         <is>
           <t>W7</t>
         </is>
       </c>
-      <c r="C31" s="22" t="inlineStr">
+      <c r="D31" s="24" t="inlineStr">
         <is>
           <t>• 【03】Legal Hold：Hold/Release + 处置豁免 + 留痕</t>
         </is>
       </c>
-      <c r="D31" s="23" t="inlineStr">
-        <is>
-          <t>Hold 可用；加密生效；驻留核查过</t>
-        </is>
-      </c>
-      <c r="E31" s="24" t="inlineStr">
+      <c r="E31" s="25" t="inlineStr">
+        <is>
+          <t>Hold 可用；加密生效；驻留过</t>
+        </is>
+      </c>
+      <c r="F31" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="25" t="inlineStr">
+      <c r="G31" s="11" t="inlineStr">
         <is>
           <t>配置模板</t>
         </is>
@@ -1632,190 +1784,213 @@
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="26" t="n"/>
       <c r="B32" s="26" t="n"/>
-      <c r="C32" s="22" t="inlineStr">
-        <is>
-          <t>• 【03】归档模型管理（保管期限表 + 分类模型）</t>
-        </is>
-      </c>
-      <c r="D32" s="26" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>• 【03】归档模型管理（保管期限表+分类）</t>
+        </is>
+      </c>
       <c r="E32" s="26" t="n"/>
       <c r="F32" s="26" t="n"/>
-    </row>
-    <row r="33" ht="30" customHeight="1">
+      <c r="G32" s="26" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
       <c r="A33" s="26" t="n"/>
       <c r="B33" s="26" t="n"/>
-      <c r="C33" s="22" t="inlineStr">
-        <is>
-          <t>• 【04】加密体系：CMK + aes_encrypt 字段级 + 密钥轮转（Key Vault DEK/KEK）</t>
-        </is>
-      </c>
-      <c r="D33" s="26" t="n"/>
+      <c r="C33" s="26" t="n"/>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>• 【04】加密体系：CMK + 字段级 + 密钥轮转</t>
+        </is>
+      </c>
       <c r="E33" s="26" t="n"/>
       <c r="F33" s="26" t="n"/>
+      <c r="G33" s="26" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
       <c r="A34" s="26" t="n"/>
       <c r="B34" s="26" t="n"/>
-      <c r="C34" s="22" t="inlineStr">
-        <is>
-          <t>• 【04】境内驻留核查：区域配置 + 出口流量管控</t>
-        </is>
-      </c>
-      <c r="D34" s="26" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>• 【04】境内驻留核查：区域配置 + 出口流量</t>
+        </is>
+      </c>
       <c r="E34" s="26" t="n"/>
       <c r="F34" s="26" t="n"/>
+      <c r="G34" s="26" t="n"/>
     </row>
     <row r="35" ht="22" customHeight="1">
       <c r="A35" s="26" t="n"/>
       <c r="B35" s="26" t="n"/>
-      <c r="C35" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【04】ADLS 生命周期规则 + Compaction 调度配置</t>
-        </is>
-      </c>
-      <c r="D35" s="26" t="n"/>
+      <c r="C35" s="26" t="n"/>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【04】ADLS 生命周期规则 + Compaction 调度</t>
+        </is>
+      </c>
       <c r="E35" s="26" t="n"/>
       <c r="F35" s="26" t="n"/>
+      <c r="G35" s="26" t="n"/>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="28" t="inlineStr">
-        <is>
-          <t>Sprint 2</t>
-        </is>
-      </c>
-      <c r="B36" s="21" t="inlineStr">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B36" s="28" t="inlineStr">
+        <is>
+          <t>S2</t>
+        </is>
+      </c>
+      <c r="C36" s="7" t="inlineStr">
         <is>
           <t>W8</t>
         </is>
       </c>
-      <c r="C36" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 处置/Legal Hold/归档模型 界面 + 审批流</t>
-        </is>
-      </c>
-      <c r="D36" s="23" t="inlineStr">
+      <c r="D36" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 处置/Legal Hold/归档模型界面 + 审批流</t>
+        </is>
+      </c>
+      <c r="E36" s="25" t="inlineStr">
         <is>
           <t>★ 处置全链路通过；四道门禁全开</t>
         </is>
       </c>
-      <c r="E36" s="24" t="inlineStr">
+      <c r="F36" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="25" t="inlineStr">
+      <c r="G36" s="11" t="inlineStr">
         <is>
           <t>界面/用例 ×3</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="30" customHeight="1">
+    <row r="37" ht="22" customHeight="1">
       <c r="A37" s="26" t="n"/>
       <c r="B37" s="26" t="n"/>
-      <c r="C37" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 处置全链路自测：设 1 天保留期 → 到期 → Hold 拦截 → Release → 处置 → 审计留痕</t>
-        </is>
-      </c>
-      <c r="D37" s="26" t="n"/>
+      <c r="C37" s="26" t="n"/>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 处置全链路自测：1 天保留期→到期→Hold→Release→处置→审计</t>
+        </is>
+      </c>
       <c r="E37" s="26" t="n"/>
       <c r="F37" s="26" t="n"/>
+      <c r="G37" s="26" t="n"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="26" t="n"/>
       <c r="B38" s="26" t="n"/>
-      <c r="C38" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 安全测试：掩码旁路/越权（垂直/水平）用例 + 修复</t>
-        </is>
-      </c>
-      <c r="D38" s="26" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 安全测试：掩码旁路/越权用例 + 修复</t>
+        </is>
+      </c>
       <c r="E38" s="26" t="n"/>
       <c r="F38" s="26" t="n"/>
+      <c r="G38" s="26" t="n"/>
     </row>
     <row r="39" ht="22" customHeight="1">
       <c r="A39" s="26" t="n"/>
       <c r="B39" s="26" t="n"/>
-      <c r="C39" s="22" t="inlineStr">
-        <is>
-          <t>• 安全门禁③④：gitleaks + Trivy 上线（四道全开）</t>
-        </is>
-      </c>
-      <c r="D39" s="26" t="n"/>
+      <c r="C39" s="26" t="n"/>
+      <c r="D39" s="24" t="inlineStr">
+        <is>
+          <t>• 安全门禁③④：gitleaks + Trivy（四道全开）</t>
+        </is>
+      </c>
       <c r="E39" s="26" t="n"/>
       <c r="F39" s="26" t="n"/>
-    </row>
-    <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="29" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B40" s="21" t="inlineStr">
+      <c r="G39" s="26" t="n"/>
+    </row>
+    <row r="40" ht="22" customHeight="1">
+      <c r="A40" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B40" s="29" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
         <is>
           <t>W9</t>
         </is>
       </c>
-      <c r="C40" s="22" t="inlineStr">
-        <is>
-          <t>• 【01】CC 全量迁移启动：600~800 有效表分 5~8 批（批次自动执行，人盯异常与重跑）</t>
-        </is>
-      </c>
-      <c r="D40" s="23" t="inlineStr">
+      <c r="D40" s="24" t="inlineStr">
+        <is>
+          <t>• 【01】CC 全量迁移启动：600~800 有效表分 5~8 批（批次自动执行，人盯异常）</t>
+        </is>
+      </c>
+      <c r="E40" s="25" t="inlineStr">
         <is>
           <t>全量迁移过半；模板库 v2</t>
         </is>
       </c>
-      <c r="E40" s="24" t="inlineStr">
-        <is>
-          <t>CC 数据量实测（W8 末 sp_spaceused）</t>
-        </is>
-      </c>
-      <c r="F40" s="25" t="inlineStr">
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>CC 数据量实测（W8 sp_spaceused）</t>
+        </is>
+      </c>
+      <c r="G40" s="11" t="inlineStr">
         <is>
           <t>模板改写 ×2</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="30" customHeight="1">
+    <row r="41" ht="22" customHeight="1">
       <c r="A41" s="26" t="n"/>
       <c r="B41" s="26" t="n"/>
-      <c r="C41" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【07】连接器模板库：MySQL 类型映射 + 文件源（复用 SQL Server 模板 AI 改写）</t>
-        </is>
-      </c>
-      <c r="D41" s="26" t="n"/>
+      <c r="C41" s="26" t="n"/>
+      <c r="D41" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【07】连接器模板库：MySQL + 文件源（复用 SQL Server 模板 AI 改写）</t>
+        </is>
+      </c>
       <c r="E41" s="26" t="n"/>
       <c r="F41" s="26" t="n"/>
+      <c r="G41" s="26" t="n"/>
     </row>
     <row r="42" ht="22" customHeight="1">
-      <c r="A42" s="29" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B42" s="21" t="inlineStr">
+      <c r="A42" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B42" s="29" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C42" s="7" t="inlineStr">
         <is>
           <t>W10</t>
         </is>
       </c>
-      <c r="C42" s="22" t="inlineStr">
+      <c r="D42" s="24" t="inlineStr">
         <is>
           <t>• 【01】全量迁移继续 + 逐批对账</t>
         </is>
       </c>
-      <c r="D42" s="23" t="inlineStr">
+      <c r="E42" s="25" t="inlineStr">
         <is>
           <t>全量对账进行中</t>
         </is>
       </c>
-      <c r="E42" s="24" t="inlineStr">
+      <c r="F42" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F42" s="25" t="inlineStr">
+      <c r="G42" s="11" t="inlineStr">
         <is>
           <t>报表页面 ×2</t>
         </is>
@@ -1824,54 +1999,61 @@
     <row r="43" ht="22" customHeight="1">
       <c r="A43" s="26" t="n"/>
       <c r="B43" s="26" t="n"/>
-      <c r="C43" s="22" t="inlineStr">
+      <c r="C43" s="26" t="n"/>
+      <c r="D43" s="24" t="inlineStr">
         <is>
           <t>• 🤖【07】连接器运行监控与审计上报</t>
         </is>
       </c>
-      <c r="D43" s="26" t="n"/>
       <c r="E43" s="26" t="n"/>
       <c r="F43" s="26" t="n"/>
+      <c r="G43" s="26" t="n"/>
     </row>
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="26" t="n"/>
       <c r="B44" s="26" t="n"/>
-      <c r="C44" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖【06】合规报表（审计查询 + 等保/个保法对照视图 + 一键导出）</t>
-        </is>
-      </c>
-      <c r="D44" s="26" t="n"/>
+      <c r="C44" s="26" t="n"/>
+      <c r="D44" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖【06】合规报表（审计查询+等保/个保法对照+导出）</t>
+        </is>
+      </c>
       <c r="E44" s="26" t="n"/>
       <c r="F44" s="26" t="n"/>
+      <c r="G44" s="26" t="n"/>
     </row>
     <row r="45" ht="22" customHeight="1">
-      <c r="A45" s="29" t="inlineStr">
-        <is>
-          <t>Sprint 3</t>
-        </is>
-      </c>
-      <c r="B45" s="21" t="inlineStr">
+      <c r="A45" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B45" s="29" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C45" s="7" t="inlineStr">
         <is>
           <t>W11</t>
         </is>
       </c>
-      <c r="C45" s="22" t="inlineStr">
-        <is>
-          <t>• 【01】全量迁移收尾 + 全量对账报告</t>
-        </is>
-      </c>
-      <c r="D45" s="23" t="inlineStr">
-        <is>
-          <t>★ CC 全量对账 100%</t>
-        </is>
-      </c>
-      <c r="E45" s="24" t="inlineStr">
+      <c r="D45" s="24" t="inlineStr">
+        <is>
+          <t>• 【01】全量迁移收尾 + 全量对账报告（全部功能 Done）</t>
+        </is>
+      </c>
+      <c r="E45" s="25" t="inlineStr">
+        <is>
+          <t>★ CC 全量对账 100%（功能收口）</t>
+        </is>
+      </c>
+      <c r="F45" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F45" s="25" t="inlineStr">
+      <c r="G45" s="11" t="inlineStr">
         <is>
           <t>用例/回归 ×2</t>
         </is>
@@ -1880,487 +2062,587 @@
     <row r="46" ht="22" customHeight="1">
       <c r="A46" s="26" t="n"/>
       <c r="B46" s="26" t="n"/>
-      <c r="C46" s="22" t="inlineStr">
+      <c r="C46" s="26" t="n"/>
+      <c r="D46" s="24" t="inlineStr">
         <is>
           <t>• 🤖【08】行级隔离验证（越权用例全跑）</t>
         </is>
       </c>
-      <c r="D46" s="26" t="n"/>
       <c r="E46" s="26" t="n"/>
       <c r="F46" s="26" t="n"/>
+      <c r="G46" s="26" t="n"/>
     </row>
     <row r="47" ht="22" customHeight="1">
       <c r="A47" s="26" t="n"/>
       <c r="B47" s="26" t="n"/>
-      <c r="C47" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 全量回归测试（AI 用例 + 人工抽查关键路径）</t>
-        </is>
-      </c>
-      <c r="D47" s="26" t="n"/>
+      <c r="C47" s="26" t="n"/>
+      <c r="D47" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 全量回归测试（AI 用例+人工抽查）</t>
+        </is>
+      </c>
       <c r="E47" s="26" t="n"/>
       <c r="F47" s="26" t="n"/>
+      <c r="G47" s="26" t="n"/>
     </row>
     <row r="48" ht="22" customHeight="1">
-      <c r="A48" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B48" s="21" t="inlineStr">
+      <c r="A48" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B48" s="29" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
         <is>
           <t>W12</t>
         </is>
       </c>
-      <c r="C48" s="22" t="inlineStr">
-        <is>
-          <t>• 生产发布准备：Helm values 生产版 + UC 权限/掩码/生命周期/驻留 生产脚本</t>
-        </is>
-      </c>
-      <c r="D48" s="23" t="inlineStr">
-        <is>
-          <t>生产环境 8 域就绪</t>
-        </is>
-      </c>
-      <c r="E48" s="24" t="inlineStr">
-        <is>
-          <t>生产环境；审批流配置</t>
-        </is>
-      </c>
-      <c r="F48" s="25" t="inlineStr">
-        <is>
-          <t>部署脚本</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="22" customHeight="1">
+      <c r="D48" s="24" t="inlineStr">
+        <is>
+          <t>• 功能打磨：性能优化 + 遗留 Bug 清零 + UX 细节</t>
+        </is>
+      </c>
+      <c r="E48" s="25" t="inlineStr">
+        <is>
+          <t>发布包就绪；材料初稿；UAT 脚本定稿</t>
+        </is>
+      </c>
+      <c r="F48" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G48" s="11" t="inlineStr">
+        <is>
+          <t>脚本/材料 ×3</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
       <c r="A49" s="26" t="n"/>
       <c r="B49" s="26" t="n"/>
-      <c r="C49" s="22" t="inlineStr">
-        <is>
-          <t>• 生产发布执行（Azure DevOps Environments 审批）</t>
-        </is>
-      </c>
-      <c r="D49" s="26" t="n"/>
+      <c r="C49" s="26" t="n"/>
+      <c r="D49" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 生产发布包：Helm 生产 values + UC 权限/掩码/生命周期/驻留 生产脚本（一键发布就绪）</t>
+        </is>
+      </c>
       <c r="E49" s="26" t="n"/>
       <c r="F49" s="26" t="n"/>
+      <c r="G49" s="26" t="n"/>
     </row>
     <row r="50" ht="22" customHeight="1">
       <c r="A50" s="26" t="n"/>
       <c r="B50" s="26" t="n"/>
-      <c r="C50" s="22" t="inlineStr">
-        <is>
-          <t>• CC 生产全量迁移启动（分批，可跨周末）</t>
-        </is>
-      </c>
-      <c r="D50" s="26" t="n"/>
+      <c r="C50" s="26" t="n"/>
+      <c r="D50" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 审批材料包起稿（技术方案/安全评估/合规对照）</t>
+        </is>
+      </c>
       <c r="E50" s="26" t="n"/>
       <c r="F50" s="26" t="n"/>
+      <c r="G50" s="26" t="n"/>
     </row>
     <row r="51" ht="22" customHeight="1">
-      <c r="A51" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B51" s="21" t="inlineStr">
+      <c r="A51" s="26" t="n"/>
+      <c r="B51" s="26" t="n"/>
+      <c r="C51" s="26" t="n"/>
+      <c r="D51" s="24" t="inlineStr">
+        <is>
+          <t>• UAT 场景脚本定稿（8 域，业务方预读）</t>
+        </is>
+      </c>
+      <c r="E51" s="26" t="n"/>
+      <c r="F51" s="26" t="n"/>
+      <c r="G51" s="26" t="n"/>
+    </row>
+    <row r="52" ht="22" customHeight="1">
+      <c r="A52" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B52" s="29" t="inlineStr">
+        <is>
+          <t>S3</t>
+        </is>
+      </c>
+      <c r="C52" s="7" t="inlineStr">
         <is>
           <t>W13</t>
         </is>
       </c>
-      <c r="C51" s="22" t="inlineStr">
-        <is>
-          <t>• CC 生产全量迁移完成 + 对账</t>
-        </is>
-      </c>
-      <c r="D51" s="23" t="inlineStr">
-        <is>
-          <t>生产全量入湖；UAT 排期确认</t>
-        </is>
-      </c>
-      <c r="E51" s="24" t="inlineStr">
-        <is>
-          <t>UAT 业务方时间</t>
-        </is>
-      </c>
-      <c r="F51" s="25" t="inlineStr">
-        <is>
-          <t>整改辅助</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="26" t="n"/>
-      <c r="B52" s="26" t="n"/>
-      <c r="C52" s="22" t="inlineStr">
-        <is>
-          <t>• 安全终检：四道门禁生产版全过 + 渗透测试配合</t>
-        </is>
-      </c>
-      <c r="D52" s="26" t="n"/>
-      <c r="E52" s="26" t="n"/>
-      <c r="F52" s="26" t="n"/>
+      <c r="D52" s="24" t="inlineStr">
+        <is>
+          <t>• UAT 预演：Staging 按 8 域脚本全走查（业务方提前介入）</t>
+        </is>
+      </c>
+      <c r="E52" s="25" t="inlineStr">
+        <is>
+          <t>★ 上线就绪检查 100% 通过（W14 上线的前置条件）</t>
+        </is>
+      </c>
+      <c r="F52" s="10" t="inlineStr">
+        <is>
+          <t>业务方预演参与；渗透排期</t>
+        </is>
+      </c>
+      <c r="G52" s="11" t="inlineStr">
+        <is>
+          <t>检查单生成</t>
+        </is>
+      </c>
     </row>
     <row r="53" ht="22" customHeight="1">
       <c r="A53" s="26" t="n"/>
       <c r="B53" s="26" t="n"/>
-      <c r="C53" s="22" t="inlineStr">
-        <is>
-          <t>• UAT 组织（业务方排期 + 环境准备）</t>
-        </is>
-      </c>
-      <c r="D53" s="26" t="n"/>
+      <c r="C53" s="26" t="n"/>
+      <c r="D53" s="24" t="inlineStr">
+        <is>
+          <t>• 安全终检：四门禁生产版全过 + 渗透测试配合</t>
+        </is>
+      </c>
       <c r="E53" s="26" t="n"/>
       <c r="F53" s="26" t="n"/>
+      <c r="G53" s="26" t="n"/>
     </row>
     <row r="54" ht="22" customHeight="1">
-      <c r="A54" s="30" t="inlineStr">
-        <is>
-          <t>Sprint 4</t>
-        </is>
-      </c>
-      <c r="B54" s="21" t="inlineStr">
-        <is>
-          <t>W14</t>
-        </is>
-      </c>
-      <c r="C54" s="22" t="inlineStr">
-        <is>
-          <t>• UAT 执行（8 域场景走查 + 记录）</t>
-        </is>
-      </c>
-      <c r="D54" s="23" t="inlineStr">
-        <is>
-          <t>★ Go-Live + UAT 签字</t>
-        </is>
-      </c>
-      <c r="E54" s="24" t="inlineStr">
-        <is>
-          <t>审批方周期</t>
-        </is>
-      </c>
-      <c r="F54" s="25" t="inlineStr">
-        <is>
-          <t>材料起草 ×3</t>
-        </is>
-      </c>
+      <c r="A54" s="26" t="n"/>
+      <c r="B54" s="26" t="n"/>
+      <c r="C54" s="26" t="n"/>
+      <c r="D54" s="24" t="inlineStr">
+        <is>
+          <t>• 生产迁移预跑 + 窗口预约（W13 晚或 W14 周末执行全量）</t>
+        </is>
+      </c>
+      <c r="E54" s="26" t="n"/>
+      <c r="F54" s="26" t="n"/>
+      <c r="G54" s="26" t="n"/>
     </row>
     <row r="55" ht="22" customHeight="1">
       <c r="A55" s="26" t="n"/>
       <c r="B55" s="26" t="n"/>
-      <c r="C55" s="22" t="inlineStr">
-        <is>
-          <t>• UAT 问题修复（P1 当日清）</t>
-        </is>
-      </c>
-      <c r="D55" s="26" t="n"/>
+      <c r="C55" s="26" t="n"/>
+      <c r="D55" s="24" t="inlineStr">
+        <is>
+          <t>• 上线就绪检查：发布包/材料/预演/回退预案 全绿</t>
+        </is>
+      </c>
       <c r="E55" s="26" t="n"/>
       <c r="F55" s="26" t="n"/>
+      <c r="G55" s="26" t="n"/>
     </row>
     <row r="56" ht="22" customHeight="1">
-      <c r="A56" s="26" t="n"/>
-      <c r="B56" s="26" t="n"/>
-      <c r="C56" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 审批材料包（技术方案/安全评估/合规对照）+ 提交</t>
-        </is>
-      </c>
-      <c r="D56" s="26" t="n"/>
-      <c r="E56" s="26" t="n"/>
-      <c r="F56" s="26" t="n"/>
+      <c r="A56" s="22" t="inlineStr">
+        <is>
+          <t>R1</t>
+        </is>
+      </c>
+      <c r="B56" s="30" t="inlineStr">
+        <is>
+          <t>S4</t>
+        </is>
+      </c>
+      <c r="C56" s="7" t="inlineStr">
+        <is>
+          <t>W14</t>
+        </is>
+      </c>
+      <c r="D56" s="24" t="inlineStr">
+        <is>
+          <t>• 生产发布执行（DevOps Environments 审批，就绪包一键发布）</t>
+        </is>
+      </c>
+      <c r="E56" s="25" t="inlineStr">
+        <is>
+          <t>★ Go-Live + UAT 签字 → Release 1 交付</t>
+        </is>
+      </c>
+      <c r="F56" s="10" t="inlineStr">
+        <is>
+          <t>UAT 排期；审批受理</t>
+        </is>
+      </c>
+      <c r="G56" s="11" t="inlineStr">
+        <is>
+          <t>（材料已提前生成）</t>
+        </is>
+      </c>
     </row>
     <row r="57" ht="22" customHeight="1">
       <c r="A57" s="26" t="n"/>
       <c r="B57" s="26" t="n"/>
-      <c r="C57" s="22" t="inlineStr">
-        <is>
-          <t>• Go-Live 决策 + 上线执行 + 48h 值守</t>
-        </is>
-      </c>
-      <c r="D57" s="26" t="n"/>
+      <c r="C57" s="26" t="n"/>
+      <c r="D57" s="24" t="inlineStr">
+        <is>
+          <t>• CC 生产全量迁移收尾（预跑后增量补齐+对账）</t>
+        </is>
+      </c>
       <c r="E57" s="26" t="n"/>
       <c r="F57" s="26" t="n"/>
+      <c r="G57" s="26" t="n"/>
     </row>
     <row r="58" ht="22" customHeight="1">
-      <c r="A58" s="31" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B58" s="21" t="inlineStr">
-        <is>
-          <t>W15</t>
-        </is>
-      </c>
-      <c r="C58" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 架构图×4（C4 上下文/容器/组件/部署）+ 数据流图（AI 从代码与配置反生成）</t>
-        </is>
-      </c>
-      <c r="D58" s="23" t="inlineStr">
-        <is>
-          <t>架构图 + 接口文档</t>
-        </is>
-      </c>
-      <c r="E58" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F58" s="25" t="inlineStr">
-        <is>
-          <t>文档 ×3~5</t>
-        </is>
-      </c>
+      <c r="A58" s="26" t="n"/>
+      <c r="B58" s="26" t="n"/>
+      <c r="C58" s="26" t="n"/>
+      <c r="D58" s="24" t="inlineStr">
+        <is>
+          <t>• UAT 正式执行（8 域场景，业务方签字）</t>
+        </is>
+      </c>
+      <c r="E58" s="26" t="n"/>
+      <c r="F58" s="26" t="n"/>
+      <c r="G58" s="26" t="n"/>
     </row>
     <row r="59" ht="22" customHeight="1">
       <c r="A59" s="26" t="n"/>
       <c r="B59" s="26" t="n"/>
-      <c r="C59" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 接口文档（OpenAPI 从代码自动导出）</t>
-        </is>
-      </c>
-      <c r="D59" s="26" t="n"/>
+      <c r="C59" s="26" t="n"/>
+      <c r="D59" s="24" t="inlineStr">
+        <is>
+          <t>• P1 问题当日清 + 审批材料提交</t>
+        </is>
+      </c>
       <c r="E59" s="26" t="n"/>
       <c r="F59" s="26" t="n"/>
+      <c r="G59" s="26" t="n"/>
     </row>
     <row r="60" ht="22" customHeight="1">
-      <c r="A60" s="31" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B60" s="21" t="inlineStr">
+      <c r="A60" s="26" t="n"/>
+      <c r="B60" s="26" t="n"/>
+      <c r="C60" s="26" t="n"/>
+      <c r="D60" s="24" t="inlineStr">
+        <is>
+          <t>• Go-Live 决策 + 上线 + 48h 值守</t>
+        </is>
+      </c>
+      <c r="E60" s="26" t="n"/>
+      <c r="F60" s="26" t="n"/>
+      <c r="G60" s="26" t="n"/>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="A61" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B61" s="32" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C61" s="7" t="inlineStr">
+        <is>
+          <t>W15</t>
+        </is>
+      </c>
+      <c r="D61" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 架构图×4（C4）+ 数据流图（AI 从代码与配置反生成）</t>
+        </is>
+      </c>
+      <c r="E61" s="25" t="inlineStr">
+        <is>
+          <t>架构图 + 接口文档</t>
+        </is>
+      </c>
+      <c r="F61" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>文档 ×3~5</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="A62" s="26" t="n"/>
+      <c r="B62" s="26" t="n"/>
+      <c r="C62" s="26" t="n"/>
+      <c r="D62" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 接口文档（OpenAPI 自动导出）</t>
+        </is>
+      </c>
+      <c r="E62" s="26" t="n"/>
+      <c r="F62" s="26" t="n"/>
+      <c r="G62" s="26" t="n"/>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B63" s="32" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
         <is>
           <t>W16</t>
         </is>
       </c>
-      <c r="C60" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 详细设计×3（应用/数据/安全）——从 git 提交记录与 ADR 还原</t>
-        </is>
-      </c>
-      <c r="D60" s="23" t="inlineStr">
+      <c r="D63" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 详细设计×3（应用/数据/安全）——从提交记录与 ADR 还原</t>
+        </is>
+      </c>
+      <c r="E63" s="25" t="inlineStr">
         <is>
           <t>详细设计 + 数据字典</t>
         </is>
       </c>
-      <c r="E60" s="24" t="inlineStr">
+      <c r="F63" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F60" s="25" t="inlineStr">
+      <c r="G63" s="11" t="inlineStr">
         <is>
           <t>文档 ×3~5</t>
         </is>
       </c>
-    </row>
-    <row r="61" ht="22" customHeight="1">
-      <c r="A61" s="26" t="n"/>
-      <c r="B61" s="26" t="n"/>
-      <c r="C61" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 数据字典（35 表 + 湖仓四层，脚本自动导出 + AI 注释）</t>
-        </is>
-      </c>
-      <c r="D61" s="26" t="n"/>
-      <c r="E61" s="26" t="n"/>
-      <c r="F61" s="26" t="n"/>
-    </row>
-    <row r="62" ht="22" customHeight="1">
-      <c r="A62" s="31" t="inlineStr">
-        <is>
-          <t>Sprint 5</t>
-        </is>
-      </c>
-      <c r="B62" s="21" t="inlineStr">
-        <is>
-          <t>W17</t>
-        </is>
-      </c>
-      <c r="C62" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 用户手册（含操作截图）+ 运维手册（部署/监控/故障/备份恢复）</t>
-        </is>
-      </c>
-      <c r="D62" s="23" t="inlineStr">
-        <is>
-          <t>★ 7 套文档终版归档</t>
-        </is>
-      </c>
-      <c r="E62" s="24" t="inlineStr">
-        <is>
-          <t>文档确认排期</t>
-        </is>
-      </c>
-      <c r="F62" s="25" t="inlineStr">
-        <is>
-          <t>文档 ×3~5</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="22" customHeight="1">
-      <c r="A63" s="26" t="n"/>
-      <c r="B63" s="26" t="n"/>
-      <c r="C63" s="22" t="inlineStr">
-        <is>
-          <t>• 🤖 培训视频（录屏 + AI 字幕）</t>
-        </is>
-      </c>
-      <c r="D63" s="26" t="n"/>
-      <c r="E63" s="26" t="n"/>
-      <c r="F63" s="26" t="n"/>
     </row>
     <row r="64" ht="22" customHeight="1">
       <c r="A64" s="26" t="n"/>
       <c r="B64" s="26" t="n"/>
-      <c r="C64" s="22" t="inlineStr">
-        <is>
-          <t>• 文档业务方/审批方确认</t>
-        </is>
-      </c>
-      <c r="D64" s="26" t="n"/>
+      <c r="C64" s="26" t="n"/>
+      <c r="D64" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 数据字典（35 表 + 湖仓四层）</t>
+        </is>
+      </c>
       <c r="E64" s="26" t="n"/>
       <c r="F64" s="26" t="n"/>
+      <c r="G64" s="26" t="n"/>
     </row>
     <row r="65" ht="22" customHeight="1">
-      <c r="A65" s="32" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B65" s="21" t="inlineStr">
-        <is>
-          <t>W18</t>
-        </is>
-      </c>
-      <c r="C65" s="22" t="inlineStr">
-        <is>
-          <t>• 缓冲：吸收全量迁移/UAT/审批任一延期</t>
-        </is>
-      </c>
-      <c r="D65" s="23" t="inlineStr">
-        <is>
-          <t>缓冲消耗报告</t>
-        </is>
-      </c>
-      <c r="E65" s="24" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F65" s="25" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="A65" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B65" s="32" t="inlineStr">
+        <is>
+          <t>S5</t>
+        </is>
+      </c>
+      <c r="C65" s="7" t="inlineStr">
+        <is>
+          <t>W17</t>
+        </is>
+      </c>
+      <c r="D65" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 用户手册（含截图）+ 运维手册（部署/监控/故障/备份恢复）</t>
+        </is>
+      </c>
+      <c r="E65" s="25" t="inlineStr">
+        <is>
+          <t>★ 7 套文档终版归档</t>
+        </is>
+      </c>
+      <c r="F65" s="10" t="inlineStr">
+        <is>
+          <t>文档确认排期</t>
+        </is>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>文档 ×3~5</t>
         </is>
       </c>
     </row>
     <row r="66" ht="22" customHeight="1">
       <c r="A66" s="26" t="n"/>
       <c r="B66" s="26" t="n"/>
-      <c r="C66" s="22" t="inlineStr">
-        <is>
-          <t>• 若无延期：遗留 Bug 清零 + 性能打磨</t>
-        </is>
-      </c>
-      <c r="D66" s="26" t="n"/>
+      <c r="C66" s="26" t="n"/>
+      <c r="D66" s="24" t="inlineStr">
+        <is>
+          <t>• 🤖 培训视频（录屏 + AI 字幕）</t>
+        </is>
+      </c>
       <c r="E66" s="26" t="n"/>
       <c r="F66" s="26" t="n"/>
+      <c r="G66" s="26" t="n"/>
     </row>
     <row r="67" ht="22" customHeight="1">
-      <c r="A67" s="32" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B67" s="21" t="inlineStr">
+      <c r="A67" s="26" t="n"/>
+      <c r="B67" s="26" t="n"/>
+      <c r="C67" s="26" t="n"/>
+      <c r="D67" s="24" t="inlineStr">
+        <is>
+          <t>• 文档业务方/审批方确认</t>
+        </is>
+      </c>
+      <c r="E67" s="26" t="n"/>
+      <c r="F67" s="26" t="n"/>
+      <c r="G67" s="26" t="n"/>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="A68" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B68" s="33" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C68" s="7" t="inlineStr">
+        <is>
+          <t>W18</t>
+        </is>
+      </c>
+      <c r="D68" s="24" t="inlineStr">
+        <is>
+          <t>• 缓冲：吸收全量迁移/UAT/审批/上线任一延期</t>
+        </is>
+      </c>
+      <c r="E68" s="25" t="inlineStr">
+        <is>
+          <t>缓冲消耗报告</t>
+        </is>
+      </c>
+      <c r="F68" s="10" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="A69" s="26" t="n"/>
+      <c r="B69" s="26" t="n"/>
+      <c r="C69" s="26" t="n"/>
+      <c r="D69" s="24" t="inlineStr">
+        <is>
+          <t>• 若无延期：遗留清零 + 性能打磨</t>
+        </is>
+      </c>
+      <c r="E69" s="26" t="n"/>
+      <c r="F69" s="26" t="n"/>
+      <c r="G69" s="26" t="n"/>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="A70" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B70" s="33" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C70" s="7" t="inlineStr">
         <is>
           <t>W19</t>
         </is>
       </c>
-      <c r="C67" s="22" t="inlineStr">
+      <c r="D70" s="24" t="inlineStr">
         <is>
           <t>• 缓冲续 / 遗留清零</t>
         </is>
       </c>
-      <c r="D67" s="23" t="inlineStr">
+      <c r="E70" s="25" t="inlineStr">
         <is>
           <t>版本 tag 就绪</t>
         </is>
       </c>
-      <c r="E67" s="24" t="inlineStr">
+      <c r="F70" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F67" s="25" t="inlineStr">
+      <c r="G70" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="22" customHeight="1">
-      <c r="A68" s="26" t="n"/>
-      <c r="B68" s="26" t="n"/>
-      <c r="C68" s="22" t="inlineStr">
+    <row r="71" ht="22" customHeight="1">
+      <c r="A71" s="26" t="n"/>
+      <c r="B71" s="26" t="n"/>
+      <c r="C71" s="26" t="n"/>
+      <c r="D71" s="24" t="inlineStr">
         <is>
           <t>• 交付物整理：代码/脚本/文档 版本 tag</t>
         </is>
       </c>
-      <c r="D68" s="26" t="n"/>
-      <c r="E68" s="26" t="n"/>
-      <c r="F68" s="26" t="n"/>
-    </row>
-    <row r="69" ht="22" customHeight="1">
-      <c r="A69" s="32" t="inlineStr">
-        <is>
-          <t>Sprint 6</t>
-        </is>
-      </c>
-      <c r="B69" s="21" t="inlineStr">
+      <c r="E71" s="26" t="n"/>
+      <c r="F71" s="26" t="n"/>
+      <c r="G71" s="26" t="n"/>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="A72" s="31" t="inlineStr">
+        <is>
+          <t>R2</t>
+        </is>
+      </c>
+      <c r="B72" s="33" t="inlineStr">
+        <is>
+          <t>S6</t>
+        </is>
+      </c>
+      <c r="C72" s="7" t="inlineStr">
         <is>
           <t>W20</t>
         </is>
       </c>
-      <c r="C69" s="22" t="inlineStr">
+      <c r="D72" s="24" t="inlineStr">
         <is>
           <t>• 最终自查：8 域功能 + 7 套文档 + Checklist</t>
         </is>
       </c>
-      <c r="D69" s="23" t="inlineStr">
+      <c r="E72" s="25" t="inlineStr">
         <is>
           <t>★ 项目结束</t>
         </is>
       </c>
-      <c r="E69" s="24" t="inlineStr">
+      <c r="F72" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F69" s="25" t="inlineStr">
+      <c r="G72" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="70" ht="22" customHeight="1">
-      <c r="A70" s="26" t="n"/>
-      <c r="B70" s="26" t="n"/>
-      <c r="C70" s="22" t="inlineStr">
+    <row r="73" ht="22" customHeight="1">
+      <c r="A73" s="26" t="n"/>
+      <c r="B73" s="26" t="n"/>
+      <c r="C73" s="26" t="n"/>
+      <c r="D73" s="24" t="inlineStr">
         <is>
           <t>• 项目结束</t>
         </is>
       </c>
-      <c r="D70" s="26" t="n"/>
-      <c r="E70" s="26" t="n"/>
-      <c r="F70" s="26" t="n"/>
+      <c r="E73" s="26" t="n"/>
+      <c r="F73" s="26" t="n"/>
+      <c r="G73" s="26" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
